--- a/src/assets/Template.xlsx
+++ b/src/assets/Template.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\muham\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1ccda1c60a649616/Documents/Muhammed/Coding/Projects/Khanqah/Screens/masjid-timetable/src/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DFC4959-781C-4512-B560-FC31B9BA90B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -459,19 +459,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -483,8 +471,20 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -819,57 +819,57 @@
   <sheetData>
     <row r="1" spans="1:21" ht="2.25" customHeight="1" thickBot="1"/>
     <row r="2" spans="1:21" ht="33.75" customHeight="1">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8" t="s">
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="8" t="s">
+      <c r="E2" s="12"/>
+      <c r="F2" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="7"/>
-      <c r="H2" s="9" t="s">
+      <c r="G2" s="12"/>
+      <c r="H2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="10"/>
+      <c r="J2" s="14"/>
       <c r="K2" s="3"/>
     </row>
     <row r="3" spans="1:21" ht="30" customHeight="1" thickBot="1">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="J3" s="13" t="s">
+      <c r="J3" s="9" t="s">
         <v>1</v>
       </c>
       <c r="K3" s="3"/>
@@ -888,167 +888,167 @@
       <c r="K4" s="3"/>
     </row>
     <row r="5" spans="1:21" ht="33" customHeight="1">
-      <c r="A5" s="14">
+      <c r="A5" s="10">
         <v>0.19375000000000003</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="10">
         <v>0.23958333333333334</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="10">
         <v>0.25763888888888892</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="10">
         <v>4.5833333333333393E-2</v>
       </c>
-      <c r="E5" s="14">
-        <v>6.25E-2</v>
-      </c>
-      <c r="F5" s="14">
+      <c r="E5" s="10">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F5" s="10">
         <v>0.23611111111111116</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="10">
         <v>0.27083333333333331</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="10">
         <v>0.32638888888888895</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="10">
         <v>0.37569444444444455</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="10">
         <v>0.40625</v>
       </c>
       <c r="K5" s="3"/>
     </row>
     <row r="6" spans="1:21" ht="33" customHeight="1">
-      <c r="A6" s="14">
+      <c r="A6" s="10">
         <v>0.19444444444444448</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="10">
         <v>0.23958333333333334</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="10">
         <v>0.25833333333333336</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="10">
         <v>4.513888888888884E-2</v>
       </c>
-      <c r="E6" s="14">
-        <v>6.25E-2</v>
-      </c>
-      <c r="F6" s="14">
+      <c r="E6" s="10">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F6" s="10">
         <v>0.23472222222222217</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="10">
         <v>0.27083333333333331</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="10">
         <v>0.32430555555555562</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="10">
         <v>0.37361111111111123</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="10">
         <v>0.40625</v>
       </c>
       <c r="K6" s="3"/>
     </row>
     <row r="7" spans="1:21" ht="33" customHeight="1">
-      <c r="A7" s="14">
+      <c r="A7" s="10">
         <v>0.19583333333333336</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="10">
         <v>0.23958333333333334</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="10">
         <v>0.25972222222222224</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="10">
         <v>4.513888888888884E-2</v>
       </c>
-      <c r="E7" s="14">
-        <v>6.25E-2</v>
-      </c>
-      <c r="F7" s="14">
+      <c r="E7" s="10">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F7" s="10">
         <v>0.23402777777777783</v>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="10">
         <v>0.27083333333333331</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="10">
         <v>0.32291666666666663</v>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="10">
         <v>0.37222222222222223</v>
       </c>
-      <c r="J7" s="14">
+      <c r="J7" s="10">
         <v>0.40625</v>
       </c>
       <c r="K7" s="3"/>
       <c r="O7"/>
     </row>
     <row r="8" spans="1:21" ht="33" customHeight="1">
-      <c r="A8" s="14">
+      <c r="A8" s="10">
         <v>0.1965277777777778</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="10">
         <v>0.23958333333333334</v>
       </c>
-      <c r="C8" s="14">
-        <v>0.26041666666666669</v>
-      </c>
-      <c r="D8" s="14">
+      <c r="C8" s="10">
+        <v>0.26041666666666669</v>
+      </c>
+      <c r="D8" s="10">
         <v>4.513888888888884E-2</v>
       </c>
-      <c r="E8" s="14">
-        <v>6.25E-2</v>
-      </c>
-      <c r="F8" s="14">
+      <c r="E8" s="10">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F8" s="10">
         <v>0.23263888888888884</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="10">
         <v>0.27083333333333331</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="10">
         <v>0.32152777777777786</v>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="10">
         <v>0.3715277777777779</v>
       </c>
-      <c r="J8" s="14">
+      <c r="J8" s="10">
         <v>0.40625</v>
       </c>
       <c r="K8" s="3"/>
     </row>
     <row r="9" spans="1:21" ht="33" customHeight="1">
-      <c r="A9" s="14">
+      <c r="A9" s="10">
         <v>0.19791666666666669</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="10">
         <v>0.25</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="10">
         <v>0.26180555555555557</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="10">
         <v>4.4444444444444398E-2</v>
       </c>
-      <c r="E9" s="14">
-        <v>6.25E-2</v>
-      </c>
-      <c r="F9" s="14">
+      <c r="E9" s="10">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F9" s="10">
         <v>0.23125000000000007</v>
       </c>
-      <c r="G9" s="14">
-        <v>0.26041666666666669</v>
-      </c>
-      <c r="H9" s="14">
+      <c r="G9" s="10">
+        <v>0.26041666666666669</v>
+      </c>
+      <c r="H9" s="10">
         <v>0.32013888888888886</v>
       </c>
-      <c r="I9" s="14">
+      <c r="I9" s="10">
         <v>0.37013888888888891</v>
       </c>
-      <c r="J9" s="14">
+      <c r="J9" s="10">
         <v>0.39583333333333331</v>
       </c>
       <c r="K9" s="3"/>
@@ -1057,101 +1057,101 @@
       </c>
     </row>
     <row r="10" spans="1:21" ht="33" customHeight="1">
-      <c r="A10" s="14">
+      <c r="A10" s="10">
         <v>0.19861111111111113</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="10">
         <v>0.25</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="10">
         <v>0.26250000000000001</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="10">
         <v>4.4444444444444398E-2</v>
       </c>
-      <c r="E10" s="14">
-        <v>6.25E-2</v>
-      </c>
-      <c r="F10" s="14">
+      <c r="E10" s="10">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F10" s="10">
         <v>0.22986111111111107</v>
       </c>
-      <c r="G10" s="14">
-        <v>0.26041666666666669</v>
-      </c>
-      <c r="H10" s="14">
+      <c r="G10" s="10">
+        <v>0.26041666666666669</v>
+      </c>
+      <c r="H10" s="10">
         <v>0.31805555555555554</v>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="10">
         <v>0.36805555555555558</v>
       </c>
-      <c r="J10" s="14">
+      <c r="J10" s="10">
         <v>0.39583333333333331</v>
       </c>
       <c r="K10" s="3"/>
       <c r="Q10"/>
     </row>
     <row r="11" spans="1:21" ht="33" customHeight="1">
-      <c r="A11" s="14">
+      <c r="A11" s="10">
         <v>0.2</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="10">
         <v>0.25</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="10">
         <v>0.2638888888888889</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="10">
         <v>4.4444444444444398E-2</v>
       </c>
-      <c r="E11" s="14">
-        <v>6.25E-2</v>
-      </c>
-      <c r="F11" s="14">
+      <c r="E11" s="10">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F11" s="10">
         <v>0.22916666666666663</v>
       </c>
-      <c r="G11" s="14">
-        <v>0.26041666666666669</v>
-      </c>
-      <c r="H11" s="14">
+      <c r="G11" s="10">
+        <v>0.26041666666666669</v>
+      </c>
+      <c r="H11" s="10">
         <v>0.31666666666666665</v>
       </c>
-      <c r="I11" s="14">
+      <c r="I11" s="10">
         <v>0.36736111111111114</v>
       </c>
-      <c r="J11" s="14">
+      <c r="J11" s="10">
         <v>0.39583333333333331</v>
       </c>
       <c r="K11" s="3"/>
     </row>
     <row r="12" spans="1:21" ht="33" customHeight="1">
-      <c r="A12" s="14">
+      <c r="A12" s="10">
         <v>0.2013888888888889</v>
       </c>
-      <c r="B12" s="14">
+      <c r="B12" s="10">
         <v>0.25</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="10">
         <v>0.26527777777777778</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="10">
         <v>4.3749999999999956E-2</v>
       </c>
-      <c r="E12" s="14">
-        <v>6.25E-2</v>
-      </c>
-      <c r="F12" s="14">
+      <c r="E12" s="10">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F12" s="10">
         <v>0.22777777777777775</v>
       </c>
-      <c r="G12" s="14">
-        <v>0.26041666666666669</v>
-      </c>
-      <c r="H12" s="14">
+      <c r="G12" s="10">
+        <v>0.26041666666666669</v>
+      </c>
+      <c r="H12" s="10">
         <v>0.31527777777777777</v>
       </c>
-      <c r="I12" s="14">
+      <c r="I12" s="10">
         <v>0.36597222222222225</v>
       </c>
-      <c r="J12" s="14">
+      <c r="J12" s="10">
         <v>0.39583333333333331</v>
       </c>
       <c r="K12" s="3"/>
@@ -1163,67 +1163,67 @@
       </c>
     </row>
     <row r="13" spans="1:21" ht="33" customHeight="1">
-      <c r="A13" s="14">
+      <c r="A13" s="10">
         <v>0.20208333333333334</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="10">
         <v>0.25</v>
       </c>
-      <c r="C13" s="14">
+      <c r="C13" s="10">
         <v>0.26597222222222222</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="10">
         <v>4.3749999999999956E-2</v>
       </c>
-      <c r="E13" s="14">
-        <v>6.25E-2</v>
-      </c>
-      <c r="F13" s="14">
+      <c r="E13" s="10">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F13" s="10">
         <v>0.22638888888888886</v>
       </c>
-      <c r="G13" s="14">
-        <v>0.26041666666666669</v>
-      </c>
-      <c r="H13" s="14">
+      <c r="G13" s="10">
+        <v>0.26041666666666669</v>
+      </c>
+      <c r="H13" s="10">
         <v>0.31388888888888888</v>
       </c>
-      <c r="I13" s="14">
+      <c r="I13" s="10">
         <v>0.36458333333333337</v>
       </c>
-      <c r="J13" s="14">
+      <c r="J13" s="10">
         <v>0.39583333333333331</v>
       </c>
       <c r="K13" s="3"/>
     </row>
     <row r="14" spans="1:21" ht="33" customHeight="1">
-      <c r="A14" s="14">
+      <c r="A14" s="10">
         <v>0.20347222222222222</v>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="10">
         <v>0.25</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="10">
         <v>0.2673611111111111</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="10">
         <v>4.3749999999999956E-2</v>
       </c>
-      <c r="E14" s="14">
-        <v>6.25E-2</v>
-      </c>
-      <c r="F14" s="14">
+      <c r="E14" s="10">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F14" s="10">
         <v>0.22499999999999998</v>
       </c>
-      <c r="G14" s="14">
-        <v>0.26041666666666669</v>
-      </c>
-      <c r="H14" s="14">
+      <c r="G14" s="10">
+        <v>0.26041666666666669</v>
+      </c>
+      <c r="H14" s="10">
         <v>0.31180555555555556</v>
       </c>
-      <c r="I14" s="14">
+      <c r="I14" s="10">
         <v>0.36250000000000004</v>
       </c>
-      <c r="J14" s="14">
+      <c r="J14" s="10">
         <v>0.39583333333333331</v>
       </c>
       <c r="K14" s="3"/>
@@ -1232,34 +1232,34 @@
       </c>
     </row>
     <row r="15" spans="1:21" ht="33" customHeight="1">
-      <c r="A15" s="14">
+      <c r="A15" s="10">
         <v>0.20416666666666666</v>
       </c>
-      <c r="B15" s="14">
+      <c r="B15" s="10">
         <v>0.25</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="10">
         <v>0.26805555555555555</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="10">
         <v>4.3055555555555514E-2</v>
       </c>
-      <c r="E15" s="14">
-        <v>6.25E-2</v>
-      </c>
-      <c r="F15" s="14">
+      <c r="E15" s="10">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F15" s="10">
         <v>0.22361111111111109</v>
       </c>
-      <c r="G15" s="14">
-        <v>0.26041666666666669</v>
-      </c>
-      <c r="H15" s="14">
+      <c r="G15" s="10">
+        <v>0.26041666666666669</v>
+      </c>
+      <c r="H15" s="10">
         <v>0.31041666666666656</v>
       </c>
-      <c r="I15" s="14">
+      <c r="I15" s="10">
         <v>0.36180555555555549</v>
       </c>
-      <c r="J15" s="14">
+      <c r="J15" s="10">
         <v>0.39583333333333331</v>
       </c>
       <c r="K15" s="3"/>
@@ -1271,34 +1271,34 @@
       </c>
     </row>
     <row r="16" spans="1:21" ht="33" customHeight="1">
-      <c r="A16" s="14">
+      <c r="A16" s="10">
         <v>0.20555555555555555</v>
       </c>
-      <c r="B16" s="14">
-        <v>0.26041666666666669</v>
-      </c>
-      <c r="C16" s="14">
+      <c r="B16" s="10">
+        <v>0.26041666666666669</v>
+      </c>
+      <c r="C16" s="10">
         <v>0.26944444444444443</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="10">
         <v>4.3055555555555514E-2</v>
       </c>
-      <c r="E16" s="14">
-        <v>6.25E-2</v>
-      </c>
-      <c r="F16" s="14">
+      <c r="E16" s="10">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F16" s="10">
         <v>0.22222222222222221</v>
       </c>
-      <c r="G16" s="14">
+      <c r="G16" s="10">
         <v>0.25</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H16" s="10">
         <v>0.30902777777777779</v>
       </c>
-      <c r="I16" s="14">
+      <c r="I16" s="10">
         <v>0.36041666666666672</v>
       </c>
-      <c r="J16" s="14">
+      <c r="J16" s="10">
         <v>0.38541666666666669</v>
       </c>
       <c r="K16" s="3"/>
@@ -1310,34 +1310,34 @@
       </c>
     </row>
     <row r="17" spans="1:18" ht="33" customHeight="1">
-      <c r="A17" s="14">
+      <c r="A17" s="10">
         <v>0.20694444444444443</v>
       </c>
-      <c r="B17" s="14">
-        <v>0.26041666666666669</v>
-      </c>
-      <c r="C17" s="14">
+      <c r="B17" s="10">
+        <v>0.26041666666666669</v>
+      </c>
+      <c r="C17" s="10">
         <v>0.27083333333333331</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="10">
         <v>4.3055555555555514E-2</v>
       </c>
-      <c r="E17" s="14">
-        <v>6.25E-2</v>
-      </c>
-      <c r="F17" s="14">
+      <c r="E17" s="10">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F17" s="10">
         <v>0.22083333333333333</v>
       </c>
-      <c r="G17" s="14">
+      <c r="G17" s="10">
         <v>0.25</v>
       </c>
-      <c r="H17" s="14">
+      <c r="H17" s="10">
         <v>0.30694444444444446</v>
       </c>
-      <c r="I17" s="14">
+      <c r="I17" s="10">
         <v>0.35833333333333339</v>
       </c>
-      <c r="J17" s="14">
+      <c r="J17" s="10">
         <v>0.38541666666666669</v>
       </c>
       <c r="K17" s="3"/>
@@ -1346,67 +1346,67 @@
       </c>
     </row>
     <row r="18" spans="1:18" ht="33" customHeight="1">
-      <c r="A18" s="14">
+      <c r="A18" s="10">
         <v>0.20763888888888887</v>
       </c>
-      <c r="B18" s="14">
-        <v>0.26041666666666669</v>
-      </c>
-      <c r="C18" s="14">
+      <c r="B18" s="10">
+        <v>0.26041666666666669</v>
+      </c>
+      <c r="C18" s="10">
         <v>0.27152777777777776</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="10">
         <v>4.2361111111111072E-2</v>
       </c>
-      <c r="E18" s="14">
-        <v>6.25E-2</v>
-      </c>
-      <c r="F18" s="14">
+      <c r="E18" s="10">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F18" s="10">
         <v>0.22013888888888899</v>
       </c>
-      <c r="G18" s="14">
+      <c r="G18" s="10">
         <v>0.25</v>
       </c>
-      <c r="H18" s="14">
+      <c r="H18" s="10">
         <v>0.30555555555555558</v>
       </c>
-      <c r="I18" s="14">
+      <c r="I18" s="10">
         <v>0.35694444444444451</v>
       </c>
-      <c r="J18" s="14">
+      <c r="J18" s="10">
         <v>0.38541666666666669</v>
       </c>
       <c r="K18" s="3"/>
     </row>
     <row r="19" spans="1:18" ht="33" customHeight="1">
-      <c r="A19" s="14">
+      <c r="A19" s="10">
         <v>0.20902777777777776</v>
       </c>
-      <c r="B19" s="14">
-        <v>0.26041666666666669</v>
-      </c>
-      <c r="C19" s="14">
+      <c r="B19" s="10">
+        <v>0.26041666666666669</v>
+      </c>
+      <c r="C19" s="10">
         <v>0.27291666666666664</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="10">
         <v>4.2361111111111072E-2</v>
       </c>
-      <c r="E19" s="14">
-        <v>6.25E-2</v>
-      </c>
-      <c r="F19" s="14">
+      <c r="E19" s="10">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F19" s="10">
         <v>0.21875</v>
       </c>
-      <c r="G19" s="14">
+      <c r="G19" s="10">
         <v>0.25</v>
       </c>
-      <c r="H19" s="14">
+      <c r="H19" s="10">
         <v>0.3041666666666667</v>
       </c>
-      <c r="I19" s="14">
+      <c r="I19" s="10">
         <v>0.35625000000000007</v>
       </c>
-      <c r="J19" s="14">
+      <c r="J19" s="10">
         <v>0.38541666666666669</v>
       </c>
       <c r="K19" s="3"/>
@@ -1415,166 +1415,166 @@
       </c>
     </row>
     <row r="20" spans="1:18" ht="33" customHeight="1">
-      <c r="A20" s="14">
+      <c r="A20" s="10">
         <v>0.2104166666666667</v>
       </c>
-      <c r="B20" s="14">
-        <v>0.26041666666666669</v>
-      </c>
-      <c r="C20" s="14">
+      <c r="B20" s="10">
+        <v>0.26041666666666669</v>
+      </c>
+      <c r="C20" s="10">
         <v>0.27361111111111114</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="10">
         <v>4.166666666666663E-2</v>
       </c>
-      <c r="E20" s="14">
-        <v>6.25E-2</v>
-      </c>
-      <c r="F20" s="14">
+      <c r="E20" s="10">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F20" s="10">
         <v>0.21736111111111101</v>
       </c>
-      <c r="G20" s="14">
+      <c r="G20" s="10">
         <v>0.25</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="10">
         <v>0.30208333333333326</v>
       </c>
-      <c r="I20" s="14">
+      <c r="I20" s="10">
         <v>0.35416666666666663</v>
       </c>
-      <c r="J20" s="14">
+      <c r="J20" s="10">
         <v>0.38541666666666669</v>
       </c>
       <c r="K20" s="3"/>
     </row>
     <row r="21" spans="1:18" ht="33" customHeight="1">
-      <c r="A21" s="14">
+      <c r="A21" s="10">
         <v>0.21180555555555558</v>
       </c>
-      <c r="B21" s="14">
-        <v>0.26041666666666669</v>
-      </c>
-      <c r="C21" s="14">
+      <c r="B21" s="10">
+        <v>0.26041666666666669</v>
+      </c>
+      <c r="C21" s="10">
         <v>0.27500000000000002</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="10">
         <v>4.166666666666663E-2</v>
       </c>
-      <c r="E21" s="14">
-        <v>6.25E-2</v>
-      </c>
-      <c r="F21" s="14">
+      <c r="E21" s="10">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F21" s="10">
         <v>0.21597222222222223</v>
       </c>
-      <c r="G21" s="14">
+      <c r="G21" s="10">
         <v>0.25</v>
       </c>
-      <c r="H21" s="14">
+      <c r="H21" s="10">
         <v>0.30069444444444449</v>
       </c>
-      <c r="I21" s="14">
+      <c r="I21" s="10">
         <v>0.35277777777777786</v>
       </c>
-      <c r="J21" s="14">
+      <c r="J21" s="10">
         <v>0.38541666666666669</v>
       </c>
       <c r="K21" s="3"/>
     </row>
     <row r="22" spans="1:18" ht="33" customHeight="1">
-      <c r="A22" s="14">
+      <c r="A22" s="10">
         <v>0.21319444444444446</v>
       </c>
-      <c r="B22" s="14">
-        <v>0.26041666666666669</v>
-      </c>
-      <c r="C22" s="14">
+      <c r="B22" s="10">
+        <v>0.26041666666666669</v>
+      </c>
+      <c r="C22" s="10">
         <v>0.27638888888888891</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="10">
         <v>4.166666666666663E-2</v>
       </c>
-      <c r="E22" s="14">
-        <v>6.25E-2</v>
-      </c>
-      <c r="F22" s="14">
+      <c r="E22" s="10">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F22" s="10">
         <v>0.21458333333333324</v>
       </c>
-      <c r="G22" s="14">
+      <c r="G22" s="10">
         <v>0.25</v>
       </c>
-      <c r="H22" s="14">
+      <c r="H22" s="10">
         <v>0.29930555555555549</v>
       </c>
-      <c r="I22" s="14">
+      <c r="I22" s="10">
         <v>0.35138888888888886</v>
       </c>
-      <c r="J22" s="14">
+      <c r="J22" s="10">
         <v>0.38541666666666669</v>
       </c>
       <c r="K22" s="3"/>
     </row>
     <row r="23" spans="1:18" ht="33" customHeight="1">
-      <c r="A23" s="14">
+      <c r="A23" s="10">
         <v>0.21458333333333335</v>
       </c>
-      <c r="B23" s="14">
-        <v>0.26041666666666669</v>
-      </c>
-      <c r="C23" s="14">
+      <c r="B23" s="10">
+        <v>0.26041666666666669</v>
+      </c>
+      <c r="C23" s="10">
         <v>0.27708333333333335</v>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="10">
         <v>0.54097222222222219</v>
       </c>
-      <c r="E23" s="14">
-        <v>6.25E-2</v>
-      </c>
-      <c r="F23" s="14">
+      <c r="E23" s="10">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F23" s="10">
         <v>0.21319444444444446</v>
       </c>
-      <c r="G23" s="14">
+      <c r="G23" s="10">
         <v>0.23958333333333334</v>
       </c>
-      <c r="H23" s="14">
+      <c r="H23" s="10">
         <v>0.29791666666666672</v>
       </c>
-      <c r="I23" s="14">
+      <c r="I23" s="10">
         <v>0.35000000000000009</v>
       </c>
-      <c r="J23" s="14">
+      <c r="J23" s="10">
         <v>0.375</v>
       </c>
       <c r="K23" s="3"/>
     </row>
     <row r="24" spans="1:18" s="3" customFormat="1" ht="33" customHeight="1">
-      <c r="A24" s="14">
+      <c r="A24" s="10">
         <v>0.21597222222222223</v>
       </c>
-      <c r="B24" s="14">
-        <v>0.26041666666666669</v>
-      </c>
-      <c r="C24" s="14">
+      <c r="B24" s="10">
+        <v>0.26041666666666669</v>
+      </c>
+      <c r="C24" s="10">
         <v>0.27847222222222223</v>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="10">
         <v>0.54097222222222219</v>
       </c>
-      <c r="E24" s="14">
-        <v>6.25E-2</v>
-      </c>
-      <c r="F24" s="14">
+      <c r="E24" s="10">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F24" s="10">
         <v>0.21180555555555547</v>
       </c>
-      <c r="G24" s="14">
+      <c r="G24" s="10">
         <v>0.23958333333333334</v>
       </c>
-      <c r="H24" s="14">
+      <c r="H24" s="10">
         <v>0.29583333333333339</v>
       </c>
-      <c r="I24" s="14">
+      <c r="I24" s="10">
         <v>0.34791666666666676</v>
       </c>
-      <c r="J24" s="14">
+      <c r="J24" s="10">
         <v>0.375</v>
       </c>
       <c r="L24" s="1"/>
@@ -1583,34 +1583,34 @@
       </c>
     </row>
     <row r="25" spans="1:18" ht="33" customHeight="1">
-      <c r="A25" s="14">
+      <c r="A25" s="10">
         <v>0.21666666666666667</v>
       </c>
-      <c r="B25" s="14">
-        <v>0.26041666666666669</v>
-      </c>
-      <c r="C25" s="14">
+      <c r="B25" s="10">
+        <v>0.26041666666666669</v>
+      </c>
+      <c r="C25" s="10">
         <v>0.27916666666666667</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="10">
         <v>0.54097222222222219</v>
       </c>
-      <c r="E25" s="14">
-        <v>6.25E-2</v>
-      </c>
-      <c r="F25" s="14">
+      <c r="E25" s="10">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F25" s="10">
         <v>0.2104166666666667</v>
       </c>
-      <c r="G25" s="14">
+      <c r="G25" s="10">
         <v>0.23958333333333334</v>
       </c>
-      <c r="H25" s="14">
+      <c r="H25" s="10">
         <v>0.2944444444444444</v>
       </c>
-      <c r="I25" s="14">
+      <c r="I25" s="10">
         <v>0.34722222222222221</v>
       </c>
-      <c r="J25" s="14">
+      <c r="J25" s="10">
         <v>0.375</v>
       </c>
       <c r="K25" s="3"/>
@@ -1619,34 +1619,34 @@
       </c>
     </row>
     <row r="26" spans="1:18" ht="33" customHeight="1">
-      <c r="A26" s="14">
+      <c r="A26" s="10">
         <v>0.21875</v>
       </c>
-      <c r="B26" s="14">
-        <v>0.26041666666666669</v>
-      </c>
-      <c r="C26" s="14">
+      <c r="B26" s="10">
+        <v>0.26041666666666669</v>
+      </c>
+      <c r="C26" s="10">
         <v>0.28055555555555556</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D26" s="10">
         <v>0.54027777777777775</v>
       </c>
-      <c r="E26" s="14">
-        <v>6.25E-2</v>
-      </c>
-      <c r="F26" s="14">
+      <c r="E26" s="10">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F26" s="10">
         <v>0.2090277777777777</v>
       </c>
-      <c r="G26" s="14">
+      <c r="G26" s="10">
         <v>0.23958333333333334</v>
       </c>
-      <c r="H26" s="14">
+      <c r="H26" s="10">
         <v>0.29305555555555562</v>
       </c>
-      <c r="I26" s="14">
+      <c r="I26" s="10">
         <v>0.34583333333333344</v>
       </c>
-      <c r="J26" s="14">
+      <c r="J26" s="10">
         <v>0.375</v>
       </c>
       <c r="K26" s="3"/>
@@ -1655,34 +1655,34 @@
       </c>
     </row>
     <row r="27" spans="1:18" ht="33" customHeight="1">
-      <c r="A27" s="14">
+      <c r="A27" s="10">
         <v>0.22013888888888888</v>
       </c>
-      <c r="B27" s="14">
-        <v>0.26041666666666669</v>
-      </c>
-      <c r="C27" s="14">
+      <c r="B27" s="10">
+        <v>0.26041666666666669</v>
+      </c>
+      <c r="C27" s="10">
         <v>0.28194444444444444</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="10">
         <v>0.54027777777777775</v>
       </c>
-      <c r="E27" s="14">
-        <v>6.25E-2</v>
-      </c>
-      <c r="F27" s="14">
+      <c r="E27" s="10">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F27" s="10">
         <v>0.20763888888888893</v>
       </c>
-      <c r="G27" s="14">
+      <c r="G27" s="10">
         <v>0.23958333333333334</v>
       </c>
-      <c r="H27" s="14">
+      <c r="H27" s="10">
         <v>0.29097222222222219</v>
       </c>
-      <c r="I27" s="14">
+      <c r="I27" s="10">
         <v>0.34375</v>
       </c>
-      <c r="J27" s="14">
+      <c r="J27" s="10">
         <v>0.375</v>
       </c>
       <c r="K27" s="3"/>
@@ -1694,133 +1694,133 @@
       </c>
     </row>
     <row r="28" spans="1:18" ht="33" customHeight="1">
-      <c r="A28" s="14">
+      <c r="A28" s="10">
         <v>0.22083333333333333</v>
       </c>
-      <c r="B28" s="14">
-        <v>0.26041666666666669</v>
-      </c>
-      <c r="C28" s="14">
+      <c r="B28" s="10">
+        <v>0.26041666666666669</v>
+      </c>
+      <c r="C28" s="10">
         <v>0.28263888888888888</v>
       </c>
-      <c r="D28" s="14">
+      <c r="D28" s="10">
         <v>0.54027777777777775</v>
       </c>
-      <c r="E28" s="14">
-        <v>6.25E-2</v>
-      </c>
-      <c r="F28" s="14">
+      <c r="E28" s="10">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F28" s="10">
         <v>0.20624999999999993</v>
       </c>
-      <c r="G28" s="14">
+      <c r="G28" s="10">
         <v>0.23958333333333334</v>
       </c>
-      <c r="H28" s="14">
+      <c r="H28" s="10">
         <v>0.2895833333333333</v>
       </c>
-      <c r="I28" s="14">
+      <c r="I28" s="10">
         <v>0.34236111111111112</v>
       </c>
-      <c r="J28" s="14">
+      <c r="J28" s="10">
         <v>0.375</v>
       </c>
       <c r="K28" s="3"/>
     </row>
     <row r="29" spans="1:18" ht="33" customHeight="1">
-      <c r="A29" s="14">
+      <c r="A29" s="10">
         <v>0.22291666666666671</v>
       </c>
-      <c r="B29" s="14">
-        <v>0.26041666666666669</v>
-      </c>
-      <c r="C29" s="14">
+      <c r="B29" s="10">
+        <v>0.26041666666666669</v>
+      </c>
+      <c r="C29" s="10">
         <v>0.28402777777777782</v>
       </c>
-      <c r="D29" s="14">
+      <c r="D29" s="10">
         <v>0.5395833333333333</v>
       </c>
-      <c r="E29" s="14">
-        <v>6.25E-2</v>
-      </c>
-      <c r="F29" s="14">
+      <c r="E29" s="10">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F29" s="10">
         <v>0.20486111111111116</v>
       </c>
-      <c r="G29" s="14">
+      <c r="G29" s="10">
         <v>0.23958333333333334</v>
       </c>
-      <c r="H29" s="14">
+      <c r="H29" s="10">
         <v>0.28819444444444442</v>
       </c>
-      <c r="I29" s="14">
+      <c r="I29" s="10">
         <v>0.34166666666666667</v>
       </c>
-      <c r="J29" s="14">
+      <c r="J29" s="10">
         <v>0.375</v>
       </c>
       <c r="K29" s="3"/>
     </row>
     <row r="30" spans="1:18" ht="33" customHeight="1">
-      <c r="A30" s="14">
+      <c r="A30" s="10">
         <v>0.22361111111111109</v>
       </c>
-      <c r="B30" s="14">
+      <c r="B30" s="10">
         <v>0.27083333333333331</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="10">
         <v>0.28472222222222221</v>
       </c>
-      <c r="D30" s="14">
+      <c r="D30" s="10">
         <v>0.5395833333333333</v>
       </c>
-      <c r="E30" s="14">
-        <v>6.25E-2</v>
-      </c>
-      <c r="F30" s="14">
+      <c r="E30" s="10">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F30" s="10">
         <v>0.20347222222222217</v>
       </c>
-      <c r="G30" s="14">
+      <c r="G30" s="10">
         <v>0.22916666666666666</v>
       </c>
-      <c r="H30" s="14">
+      <c r="H30" s="10">
         <v>0.28611111111111109</v>
       </c>
-      <c r="I30" s="14">
+      <c r="I30" s="10">
         <v>0.33958333333333335</v>
       </c>
-      <c r="J30" s="14">
+      <c r="J30" s="10">
         <v>0.375</v>
       </c>
       <c r="K30" s="3"/>
     </row>
     <row r="31" spans="1:18" ht="33" customHeight="1">
-      <c r="A31" s="14">
+      <c r="A31" s="10">
         <v>0.22500000000000003</v>
       </c>
-      <c r="B31" s="14">
+      <c r="B31" s="10">
         <v>0.27083333333333331</v>
       </c>
-      <c r="C31" s="14">
+      <c r="C31" s="10">
         <v>0.28611111111111115</v>
       </c>
-      <c r="D31" s="14">
+      <c r="D31" s="10">
         <v>0.5395833333333333</v>
       </c>
-      <c r="E31" s="14">
-        <v>6.25E-2</v>
-      </c>
-      <c r="F31" s="14">
+      <c r="E31" s="10">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F31" s="10">
         <v>0.20208333333333339</v>
       </c>
-      <c r="G31" s="14">
+      <c r="G31" s="10">
         <v>0.22916666666666666</v>
       </c>
-      <c r="H31" s="14">
+      <c r="H31" s="10">
         <v>0.28472222222222232</v>
       </c>
-      <c r="I31" s="14">
+      <c r="I31" s="10">
         <v>0.33819444444444458</v>
       </c>
-      <c r="J31" s="14">
+      <c r="J31" s="10">
         <v>0.375</v>
       </c>
       <c r="K31" s="3"/>
@@ -1829,67 +1829,67 @@
       </c>
     </row>
     <row r="32" spans="1:18" ht="33" customHeight="1">
-      <c r="A32" s="14">
+      <c r="A32" s="10">
         <v>0.22708333333333336</v>
       </c>
-      <c r="B32" s="14">
+      <c r="B32" s="10">
         <v>0.27083333333333331</v>
       </c>
-      <c r="C32" s="14">
+      <c r="C32" s="10">
         <v>0.28750000000000003</v>
       </c>
-      <c r="D32" s="14">
+      <c r="D32" s="10">
         <v>0.53888888888888886</v>
       </c>
-      <c r="E32" s="14">
-        <v>6.25E-2</v>
-      </c>
-      <c r="F32" s="14">
+      <c r="E32" s="10">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F32" s="10">
         <v>0.2006944444444444</v>
       </c>
-      <c r="G32" s="14">
+      <c r="G32" s="10">
         <v>0.22916666666666666</v>
       </c>
-      <c r="H32" s="14">
+      <c r="H32" s="10">
         <v>0.28333333333333333</v>
       </c>
-      <c r="I32" s="14">
+      <c r="I32" s="10">
         <v>0.33680555555555558</v>
       </c>
-      <c r="J32" s="14">
+      <c r="J32" s="10">
         <v>0.375</v>
       </c>
       <c r="K32" s="3"/>
     </row>
     <row r="33" spans="1:14" ht="33" customHeight="1">
-      <c r="A33" s="14">
+      <c r="A33" s="10">
         <v>0.2277777777777778</v>
       </c>
-      <c r="B33" s="14">
+      <c r="B33" s="10">
         <v>0.27083333333333331</v>
       </c>
-      <c r="C33" s="14">
+      <c r="C33" s="10">
         <v>0.28819444444444448</v>
       </c>
-      <c r="D33" s="14">
+      <c r="D33" s="10">
         <v>0.53888888888888886</v>
       </c>
-      <c r="E33" s="14">
-        <v>6.25E-2</v>
-      </c>
-      <c r="F33" s="14">
+      <c r="E33" s="10">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F33" s="10">
         <v>0.19930555555555562</v>
       </c>
-      <c r="G33" s="14">
+      <c r="G33" s="10">
         <v>0.22916666666666666</v>
       </c>
-      <c r="H33" s="14">
+      <c r="H33" s="10">
         <v>0.28194444444444433</v>
       </c>
-      <c r="I33" s="14">
+      <c r="I33" s="10">
         <v>0.33541666666666659</v>
       </c>
-      <c r="J33" s="14">
+      <c r="J33" s="10">
         <v>0.375</v>
       </c>
       <c r="K33" s="3"/>
@@ -1898,34 +1898,34 @@
       </c>
     </row>
     <row r="34" spans="1:14" ht="33" customHeight="1">
-      <c r="A34" s="14">
+      <c r="A34" s="10">
         <v>0.22916666666666669</v>
       </c>
-      <c r="B34" s="14">
+      <c r="B34" s="10">
         <v>0.27083333333333331</v>
       </c>
-      <c r="C34" s="14">
+      <c r="C34" s="10">
         <v>0.28958333333333336</v>
       </c>
-      <c r="D34" s="14">
+      <c r="D34" s="10">
         <v>0.53888888888888886</v>
       </c>
-      <c r="E34" s="14">
-        <v>6.25E-2</v>
-      </c>
-      <c r="F34" s="14">
+      <c r="E34" s="10">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F34" s="10">
         <v>0.19791666666666663</v>
       </c>
-      <c r="G34" s="14">
+      <c r="G34" s="10">
         <v>0.22916666666666666</v>
       </c>
-      <c r="H34" s="14">
+      <c r="H34" s="10">
         <v>0.27986111111111112</v>
       </c>
-      <c r="I34" s="14">
+      <c r="I34" s="10">
         <v>0.33333333333333337</v>
       </c>
-      <c r="J34" s="14">
+      <c r="J34" s="10">
         <v>0.375</v>
       </c>
       <c r="K34" s="3"/>
